--- a/outputs/ptf_pesos_vbp_20260727_financieras/anex-PTF-ProductividadLaboral-2025_con_calculos_CJC.xlsx
+++ b/outputs/ptf_pesos_vbp_20260727_financieras/anex-PTF-ProductividadLaboral-2025_con_calculos_CJC.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="9" r:id="R21e625c62ee64063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro 1" sheetId="25" r:id="R86aaca5a21774c0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro 2" sheetId="30" r:id="R928e4ec45d6f4ea3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC Guía" sheetId="31" r:id="Rcf36d94bf5704c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC VA total" sheetId="32" r:id="R4c3f91730bec4721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC PTF actividad" sheetId="33" r:id="R2ebd69b8ce054808"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC Pesos VBP" sheetId="34" r:id="R22192f595fc04298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC Contribuciones" sheetId="35" r:id="Rc9e9a8fda3d9432f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC Figuras" sheetId="36" r:id="R0547e1d12e334cf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice" sheetId="9" r:id="R92040d5ac1cf49b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro 1" sheetId="25" r:id="Rbce38d87738a4eb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro 2" sheetId="30" r:id="Rf93c083884d04c94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC Guía" sheetId="31" r:id="Redbae18a4ef1444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC VA total" sheetId="32" r:id="Rd45888b3944c4045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC PTF actividad" sheetId="33" r:id="Rc4dfc327c2174f99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC Pesos VBP" sheetId="34" r:id="Ra7db69fc25574c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC Contribuciones" sheetId="35" r:id="R321c634e5e594a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CJC Figuras" sheetId="36" r:id="R1a3f9076eb4e4fa1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1694,7 +1694,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2a6434406eeb454c"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra5b468c1b2bc4616"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1726,7 +1726,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7052ee720255446b"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1f7f16f25dfa49a3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1763,7 +1763,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R91ba68d398d1467f"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R3ff10b81ce94494b"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1795,7 +1795,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9a4747a2aef04ec1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rbcfe485c33d14219"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1832,7 +1832,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R78339cfb1e004185"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4b112cdbec904bcf"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1864,7 +1864,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra8068bc9a43442cd"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd0d83b7e8cda4c46"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2579,7 +2579,7 @@
     <x:hyperlink ref="B9" location="'Cuadro 2'!A1"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra16645b1da3a4039"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc1854642fb44e4c"/>
 </x:worksheet>
 </file>
 
@@ -3241,7 +3241,7 @@
     <x:hyperlink ref="G5" location="Índice!A1"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66f2c8c21aeb4f66"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re46dcb98840846e1"/>
 </x:worksheet>
 </file>
 
@@ -3977,7 +3977,7 @@
     <x:hyperlink ref="H5" location="Índice!A1"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5733163138834b47"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree2c6c3fc84349e0"/>
 </x:worksheet>
 </file>
 
